--- a/FEBRUARY 2026/OUTSTANDING KITCHEN/SURYA CIPTA NIAGA FEBRUARY 2026.xlsx
+++ b/FEBRUARY 2026/OUTSTANDING KITCHEN/SURYA CIPTA NIAGA FEBRUARY 2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17120" windowHeight="19840"/>
+    <workbookView windowWidth="16020" windowHeight="17020"/>
   </bookViews>
   <sheets>
     <sheet name="SURYA CIPTA NIAGA BALI (Beef)" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>DATE</t>
   </si>
@@ -56,16 +56,31 @@
     <t>DUE DATE</t>
   </si>
   <si>
+    <t>STATUS</t>
+  </si>
+  <si>
     <t>2602/FK-0599</t>
   </si>
   <si>
-    <t>COW MEAT</t>
+    <t>BEEF MEAT</t>
+  </si>
+  <si>
+    <t>PAID</t>
   </si>
   <si>
     <t>STRIPLOIN ICHI BROWN</t>
   </si>
   <si>
     <t>TOP SIDE BLACK ANGUS GF ONYX</t>
+  </si>
+  <si>
+    <t>2602/FK-1854</t>
+  </si>
+  <si>
+    <t>UNPAID</t>
+  </si>
+  <si>
+    <t>2602/FK-2577</t>
   </si>
 </sst>
 </file>
@@ -813,12 +828,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
@@ -826,6 +841,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -833,12 +851,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -866,12 +878,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -904,6 +937,15 @@
     <xf numFmtId="177" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -913,14 +955,44 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1206,13 +1278,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>24447</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>26352</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>2961957</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:colOff>2961322</xdr:colOff>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>682307</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1230,8 +1302,84 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm rot="16200000">
-          <a:off x="7537450" y="0"/>
-          <a:ext cx="2052955" cy="2937510"/>
+          <a:off x="7537450" y="-212090"/>
+          <a:ext cx="2052955" cy="2936240"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>40005</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>24765</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2947035</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1779905</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="ID_E40F2A81E6514CD0809307C88BFFE118" descr="PHOTO-2026-02-20-22-38-47"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="7687310" y="1747520"/>
+          <a:ext cx="1755140" cy="2907030"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>92710</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>24765</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2894965</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>560070</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="ID_9DE83CEB47DB4E2D8676A8CBF95FDB51" descr="PHOTO-2026-02-25-19-31-28"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7164070" y="4123690"/>
+          <a:ext cx="2802255" cy="1678305"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1501,7 +1649,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="19" style="1" customWidth="1"/>
@@ -1512,195 +1660,320 @@
     <col min="6" max="7" width="18.7109375" customWidth="1"/>
     <col min="8" max="8" width="22.859375" customWidth="1"/>
     <col min="9" max="9" width="15.4296875" customWidth="1"/>
+    <col min="10" max="10" width="11.875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16" customHeight="1" spans="1:9">
-      <c r="A1" s="4" t="s">
+    <row r="1" ht="16" customHeight="1" spans="1:10">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="7" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" customFormat="1" spans="1:9">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+    <row r="2" customFormat="1" ht="55" customHeight="1" spans="1:10">
+      <c r="A2" s="8">
+        <v>46059</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="11">
+        <v>5.02</v>
+      </c>
+      <c r="E2" s="28"/>
+      <c r="F2" s="29">
+        <v>150000</v>
+      </c>
+      <c r="G2" s="29">
+        <f t="shared" ref="G2:G8" si="0">F2*D2</f>
+        <v>753000</v>
+      </c>
+      <c r="H2" s="30">
+        <f>SUM(G2:G4)</f>
+        <v>8553600</v>
+      </c>
+      <c r="I2" s="41">
+        <v>46066</v>
+      </c>
+      <c r="J2" s="42" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="3" ht="55" customHeight="1" spans="1:9">
-      <c r="A3" s="9">
-        <v>46059</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="12">
-        <v>5.02</v>
-      </c>
-      <c r="E3" s="22"/>
-      <c r="F3" s="23">
+    <row r="3" ht="55" customHeight="1" spans="1:10">
+      <c r="A3" s="12"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="11">
+        <v>7.42</v>
+      </c>
+      <c r="E3" s="31"/>
+      <c r="F3" s="29">
+        <v>180000</v>
+      </c>
+      <c r="G3" s="29">
+        <f t="shared" si="0"/>
+        <v>1335600</v>
+      </c>
+      <c r="H3" s="32"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="44"/>
+    </row>
+    <row r="4" ht="55" customHeight="1" spans="1:10">
+      <c r="A4" s="14"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="11">
+        <v>25.86</v>
+      </c>
+      <c r="E4" s="33"/>
+      <c r="F4" s="29">
+        <v>250000</v>
+      </c>
+      <c r="G4" s="29">
+        <f t="shared" si="0"/>
+        <v>6465000</v>
+      </c>
+      <c r="H4" s="34"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="46"/>
+    </row>
+    <row r="5" ht="141.75" customHeight="1" spans="1:10">
+      <c r="A5" s="16">
+        <v>46072</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="18">
+        <v>17.77</v>
+      </c>
+      <c r="E5" s="17"/>
+      <c r="F5" s="35">
+        <v>180000</v>
+      </c>
+      <c r="G5" s="29">
+        <f t="shared" si="0"/>
+        <v>3198600</v>
+      </c>
+      <c r="H5" s="35">
+        <f>SUM(G5)</f>
+        <v>3198600</v>
+      </c>
+      <c r="I5" s="47">
+        <v>46079</v>
+      </c>
+      <c r="J5" s="48" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1" spans="1:10">
+      <c r="A6" s="19">
+        <v>46078</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="18">
+        <v>12.4</v>
+      </c>
+      <c r="E6" s="20"/>
+      <c r="F6" s="35">
+        <v>250000</v>
+      </c>
+      <c r="G6" s="29">
+        <f t="shared" si="0"/>
+        <v>3100000</v>
+      </c>
+      <c r="H6" s="36">
+        <f>SUM(G6:G8)</f>
+        <v>4969600</v>
+      </c>
+      <c r="I6" s="49">
+        <v>46085</v>
+      </c>
+      <c r="J6" s="50" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1" spans="1:10">
+      <c r="A7" s="22"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="18">
+        <v>6.17</v>
+      </c>
+      <c r="E7" s="23"/>
+      <c r="F7" s="35">
+        <v>180000</v>
+      </c>
+      <c r="G7" s="29">
+        <f t="shared" si="0"/>
+        <v>1110600</v>
+      </c>
+      <c r="H7" s="37"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="52"/>
+    </row>
+    <row r="8" ht="45" customHeight="1" spans="1:10">
+      <c r="A8" s="24"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="18">
+        <v>5.06</v>
+      </c>
+      <c r="E8" s="25"/>
+      <c r="F8" s="35">
         <v>150000</v>
       </c>
-      <c r="G3" s="23">
-        <f>F3*D3</f>
-        <v>753000</v>
-      </c>
-      <c r="H3" s="24">
-        <f>SUM(G3:G5)</f>
-        <v>8553600</v>
-      </c>
-      <c r="I3" s="32">
-        <v>46066</v>
-      </c>
+      <c r="G8" s="29">
+        <f t="shared" si="0"/>
+        <v>759000</v>
+      </c>
+      <c r="H8" s="38"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="54"/>
     </row>
-    <row r="4" ht="55" customHeight="1" spans="1:9">
-      <c r="A4" s="13"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="12">
-        <v>7.42</v>
-      </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="23">
-        <v>180000</v>
-      </c>
-      <c r="G4" s="23">
-        <f>F4*D4</f>
-        <v>1335600</v>
-      </c>
-      <c r="H4" s="26"/>
-      <c r="I4" s="33"/>
+    <row r="9" spans="1:10">
+      <c r="A9" s="16"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="48"/>
     </row>
-    <row r="5" ht="55" customHeight="1" spans="1:9">
-      <c r="A5" s="15"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="12">
-        <v>25.86</v>
-      </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="23">
-        <v>250000</v>
-      </c>
-      <c r="G5" s="23">
-        <f>F5*D5</f>
-        <v>6465000</v>
-      </c>
-      <c r="H5" s="28"/>
-      <c r="I5" s="34"/>
+    <row r="10" spans="1:10">
+      <c r="A10" s="16"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="48"/>
     </row>
-    <row r="6" ht="70" customHeight="1" spans="1:9">
-      <c r="A6" s="17"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="29">
-        <f>SUM(G6:G7)</f>
+    <row r="11" spans="1:10">
+      <c r="A11" s="16"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="48"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="16"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="16"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="29">
+        <f>D13*F13</f>
         <v>0</v>
       </c>
-      <c r="I6" s="35"/>
+      <c r="H13" s="35">
+        <f>SUM(D13*F13)</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="47"/>
+      <c r="J13" s="48"/>
     </row>
-    <row r="7" ht="70" customHeight="1" spans="1:9">
-      <c r="A7" s="17"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="35"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="17"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="35"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="17"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="23">
-        <f>D9*F9</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="29">
-        <f>SUM(D9*F9)</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="35"/>
-    </row>
-    <row r="10" ht="26" spans="1:9">
-      <c r="A10" s="20" t="s">
+    <row r="14" ht="26" spans="1:10">
+      <c r="A14" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="30">
-        <f>SUM(H:H)-SUMIF(I:I,"PAID*",H:H)</f>
-        <v>8553600</v>
-      </c>
-      <c r="H10" s="31"/>
-      <c r="I10" s="36"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="39">
+        <f>SUM(H:H)-SUMIF(J:J,"PAID*",H:H)</f>
+        <v>8168200</v>
+      </c>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="55"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="H3:H5"/>
-    <mergeCell ref="I3:I5"/>
+  <mergeCells count="14">
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="H6:H8"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="I6:I8"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="J6:J8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
